--- a/ig/main/ValueSet-1.2.250.1.213.1.1.5.500.xlsx
+++ b/ig/main/ValueSet-1.2.250.1.213.1.1.5.500.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="93">
   <si>
     <t>Property</t>
   </si>
@@ -75,19 +75,7 @@
     <t>Publisher</t>
   </si>
   <si>
-    <t>ANS</t>
-  </si>
-  <si>
-    <t>Contact</t>
-  </si>
-  <si>
-    <t>ANS (https://esante.gouv.fr)</t>
-  </si>
-  <si>
-    <t>Jurisdiction</t>
-  </si>
-  <si>
-    <t>France</t>
+    <t>Agence du Numérique en Santé (ANS) - 2-10 Rue d'Oradour-sur-Glane, 75015 Paris</t>
   </si>
   <si>
     <t>Description</t>
@@ -443,7 +431,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -535,43 +523,27 @@
         <v>19</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>22</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="B12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="B13" t="s" s="2">
-        <v>9</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
-      </c>
-      <c r="B14" s="2"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B15" s="2"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="2">
-        <v>26</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>27</v>
+        <v>22</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -590,82 +562,82 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -684,34 +656,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B4" t="s" s="2">
         <v>44</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -730,146 +702,146 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -888,34 +860,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B4" t="s" s="2">
         <v>44</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -934,58 +906,58 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -1004,42 +976,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B5" t="s" s="2">
         <v>44</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -1058,42 +1030,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/ig/main/ValueSet-1.2.250.1.213.1.1.5.500.xlsx
+++ b/ig/main/ValueSet-1.2.250.1.213.1.1.5.500.xlsx
@@ -9,17 +9,12 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include #0" r:id="rId4" sheetId="2"/>
     <sheet name="Include #1" r:id="rId5" sheetId="3"/>
-    <sheet name="Include #2" r:id="rId6" sheetId="4"/>
-    <sheet name="Include #3" r:id="rId7" sheetId="5"/>
-    <sheet name="Include #4" r:id="rId8" sheetId="6"/>
-    <sheet name="Include #5" r:id="rId9" sheetId="7"/>
-    <sheet name="Include #6" r:id="rId10" sheetId="8"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="93">
   <si>
     <t>Property</t>
   </si>
@@ -69,13 +64,13 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-08T01:00:00+02:00</t>
+    <t>2024-04-08T00:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>Agence du Numérique en Santé (ANS) - 2-10 Rue d'Oradour-sur-Glane, 75015 Paris</t>
+    <t>Agence du Numérique en Santé(ANS) -2 - 10 Rue d'Oradour-sur-Glane, 75015 Paris</t>
   </si>
   <si>
     <t>Description</t>
@@ -96,6 +91,39 @@
     <t>Concept</t>
   </si>
   <si>
+    <t>MED-1184</t>
+  </si>
+  <si>
+    <t>Nombre d'enfants nés vivants et décédés avant 28 jours</t>
+  </si>
+  <si>
+    <t>MED-1185</t>
+  </si>
+  <si>
+    <t>Grossesse extra-utérine</t>
+  </si>
+  <si>
+    <t>ORG-173</t>
+  </si>
+  <si>
+    <t>Projet de grossesse</t>
+  </si>
+  <si>
+    <t>MED-280</t>
+  </si>
+  <si>
+    <t>Accouchement récent</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>System URI</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/1.2.250.1.213.1.1.4.322</t>
+  </si>
+  <si>
     <t>8339-4</t>
   </si>
   <si>
@@ -138,24 +166,6 @@
     <t>Nombre d'interruptions involontaires de grossesse</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>System URI</t>
-  </si>
-  <si>
-    <t>urn:oid:2.16.840.1.113883.6.1</t>
-  </si>
-  <si>
-    <t>MED-1184</t>
-  </si>
-  <si>
-    <t>Nombre d'enfants nés vivants et décédés avant 28 jours</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/1.2.250.1.213.1.1.4.322</t>
-  </si>
-  <si>
     <t>11636-8</t>
   </si>
   <si>
@@ -246,12 +256,6 @@
     <t>Nombre de grossesses extra-utérines</t>
   </si>
   <si>
-    <t>MED-1185</t>
-  </si>
-  <si>
-    <t>Grossesse extra-utérine</t>
-  </si>
-  <si>
     <t>45371-2</t>
   </si>
   <si>
@@ -276,18 +280,6 @@
     <t>Allaitement</t>
   </si>
   <si>
-    <t>ORG-173</t>
-  </si>
-  <si>
-    <t>Projet de grossesse</t>
-  </si>
-  <si>
-    <t>MED-280</t>
-  </si>
-  <si>
-    <t>Accouchement récent</t>
-  </si>
-  <si>
     <t>42797-1</t>
   </si>
   <si>
@@ -298,6 +290,9 @@
   </si>
   <si>
     <t>Nombre de fœtus</t>
+  </si>
+  <si>
+    <t>http://loinc.org</t>
   </si>
 </sst>
 </file>
@@ -553,350 +548,6 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>24</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>27</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>29</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>41</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>24</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>44</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B18"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>24</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>45</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>49</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>51</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="2">
-        <v>53</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="2">
-        <v>55</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="2">
-        <v>57</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="2">
-        <v>59</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s" s="2">
-        <v>65</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s" s="2">
-        <v>67</v>
-      </c>
-      <c r="B13" t="s" s="2">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s" s="2">
-        <v>69</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="B18" t="s" s="2">
-        <v>41</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>24</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>44</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
@@ -914,50 +565,50 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>78</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>80</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>81</v>
+        <v>29</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>82</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>83</v>
+        <v>31</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>84</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -965,9 +616,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -984,88 +635,242 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>86</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>87</v>
+        <v>38</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>88</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B5" t="s" s="2">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
         <v>44</v>
       </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>24</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
+      <c r="B6" t="s" s="2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="B28" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="B2" t="s" s="2">
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
         <v>90</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
+      <c r="B29" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="B3" t="s" s="2">
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="B31" t="s" s="2">
         <v>92</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/ig/main/ValueSet-1.2.250.1.213.1.1.5.500.xlsx
+++ b/ig/main/ValueSet-1.2.250.1.213.1.1.5.500.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="95">
   <si>
     <t>Property</t>
   </si>
@@ -71,6 +71,12 @@
   </si>
   <si>
     <t>Agence du Numérique en Santé(ANS) -2 - 10 Rue d'Oradour-sur-Glane, 75015 Paris</t>
+  </si>
+  <si>
+    <t>Jurisdiction</t>
+  </si>
+  <si>
+    <t>France</t>
   </si>
   <si>
     <t>Description</t>
@@ -426,7 +432,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -518,27 +524,35 @@
         <v>19</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="B12" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>9</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="B14" t="s" s="2">
         <v>23</v>
+      </c>
+      <c r="B14" s="2"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -557,58 +571,58 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -627,250 +641,250 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
